--- a/d/2026-09-04_会员有效性分析.xlsx
+++ b/d/2026-09-04_会员有效性分析.xlsx
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C5" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C6" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>333</v>
+      </c>
+      <c r="C7" t="n">
         <v>332</v>
-      </c>
-      <c r="C7" t="n">
-        <v>331</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>APR成都东安天街</t>
+          <t>APR成都高新伊藤</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E40" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1726,19 +1726,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>华为北京沙河万达</t>
+          <t>APR成都东安天街</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1753,19 +1753,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DJI北京西红门荟聚中心授权体验店</t>
+          <t>华为北京沙河万达</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="E42" t="n">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DJI北京龙湖长安天街授权体验店</t>
+          <t>DJI北京西红门荟聚中心授权体验店</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="E43" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DJI北京丰科万达广场授权体验店</t>
+          <t>DJI北京龙湖长安天街授权体验店</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E44" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1834,19 +1834,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>华为北京长楹龙湖</t>
+          <t>DJI北京丰科万达广场授权体验店</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="E45" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1861,19 +1861,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>华为福州中骏世界城</t>
+          <t>华为北京长楹龙湖</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="E46" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1888,19 +1888,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>APR成都西宸天街</t>
+          <t>华为福州中骏世界城</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E47" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1915,19 +1915,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
+          <t>APR成都西宸天街</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E48" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>华为福州仓山爱琴海</t>
+          <t>DJI北京北投新奥天虹授权体验店</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1969,19 +1969,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DJI北京朝阳大悦城授权体验店</t>
+          <t>华为福州仓山爱琴海</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -1996,19 +1996,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>DJI北京朝阳大悦城授权体验店</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E51" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2023,19 +2023,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DJI北京丽泽天街授权体验店</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E52" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2050,19 +2050,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>华为福州仓山爱琴海合作店</t>
+          <t>DJI北京丽泽天街授权体验店</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E53" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>华为南平武夷山宝龙广场</t>
+          <t>华为福州仓山爱琴海合作店</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>APR成都三利爱琴海</t>
+          <t>华为南平武夷山宝龙广场</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2131,19 +2131,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>华为北京首开万象汇</t>
+          <t>APR成都三利爱琴海</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E56" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2158,19 +2158,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>APR北京常营龙湖</t>
+          <t>华为北京首开万象汇</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E57" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2185,19 +2185,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>华为福州五四北泰禾广场</t>
+          <t>APR北京常营龙湖</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E58" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2212,19 +2212,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DJI上海中庚漫游城授权体验店</t>
+          <t>华为福州五四北泰禾广场</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E59" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2239,19 +2239,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DJI北京通州万象汇授权体验店</t>
+          <t>DJI上海中庚漫游城授权体验店</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E60" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DJI北京双安商场授权体验店</t>
+          <t>DJI北京通州万象汇授权体验店</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E61" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -2293,19 +2293,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>APR北京回龙观华联</t>
+          <t>DJI北京双安商场授权体验店</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -2320,19 +2320,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DJI北京龙湖亦庄天街授权体验店</t>
+          <t>APR北京回龙观华联</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E63" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -2347,19 +2347,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>华为北京石景山万达</t>
+          <t>DJI北京龙湖亦庄天街授权体验店</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E64" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>华为北京亦庄龙湖</t>
+          <t>华为北京石景山万达</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E65" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2401,19 +2401,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DJI上海长风大悦城授权体验店</t>
+          <t>华为北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E66" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -2428,12 +2428,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>APR北京延庆万达</t>
+          <t>DJI上海长风大悦城授权体验店</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2455,19 +2455,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DJI北京昌平悦荟授权体验店</t>
+          <t>APR北京延庆万达</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E68" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DJI北京昌平超级合生汇授权体验店</t>
+          <t>DJI北京昌平悦荟授权体验店</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E69" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2509,19 +2509,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>APR北京西铁营万达</t>
+          <t>DJI北京昌平超级合生汇授权体验店</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E70" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -2536,19 +2536,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>APR成都凯德魅力城</t>
+          <t>APR北京西铁营万达</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E71" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -2563,19 +2563,19 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DJI上海虹口凯德授权体验店</t>
+          <t>APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E72" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -2590,19 +2590,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>APR北京新辰汇</t>
+          <t>DJI上海虹口凯德授权体验店</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -2617,19 +2617,19 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>APR北京新辰汇</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E74" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -2644,19 +2644,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>华为福州平潭吾悦</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -2671,19 +2671,19 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DJI北京通州万达授权体验店</t>
+          <t>华为福州平潭吾悦</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DJI北京太阳宫凯德授权体验店</t>
+          <t>DJI北京通州万达授权体验店</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -2725,19 +2725,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>APR成都龙泉吾悦</t>
+          <t>DJI北京太阳宫凯德授权体验店</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E78" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -2752,19 +2752,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>APR北京亦庄龙湖</t>
+          <t>APR成都龙泉吾悦</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E79" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -2779,19 +2779,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>APR北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E80" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2806,19 +2806,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>APR北京五道口购物中心</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E81" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -2833,19 +2833,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>APR北京五道口购物中心</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DJI上海维璟印象城授权体验店</t>
+          <t>DJI上海天荟广场授权体验店</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E83" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -2887,19 +2887,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>华为福州东街口</t>
+          <t>DJI上海维璟印象城授权体验店</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -2914,19 +2914,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DJI上海江桥万达授权体验店</t>
+          <t>华为福州东街口</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E85" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -2941,19 +2941,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>华为北京丽泽龙湖</t>
+          <t>DJI上海江桥万达授权体验店</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E86" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2968,19 +2968,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>APR北京北苑龙湖</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E87" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -2995,19 +2995,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>华为北京丽泽龙湖</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="E88" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3022,19 +3022,19 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>APR成都温江旭辉</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E89" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -3049,19 +3049,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>华为北京丰台鑫嘉汇</t>
+          <t>APR成都科华王府井</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E90" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>APR成都蜀新天街</t>
+          <t>APR成都温江旭辉</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E91" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -3103,19 +3103,19 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DJI北京东坝万达广场授权体验店</t>
+          <t>华为北京丰台鑫嘉汇</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E92" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>华为泉州石狮泰禾广场</t>
+          <t>APR成都蜀新天街</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>DJI北京东坝万达广场授权体验店</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3184,19 +3184,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
+          <t>华为泉州石狮泰禾广场</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E95" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DJI北京龙德广场授权体验店</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E96" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3238,19 +3238,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>华为厦门思明星河COCO Park</t>
+          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E97" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -3265,19 +3265,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>APR成都金牛凯德</t>
+          <t>DJI北京龙德广场授权体验店</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E98" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -3292,19 +3292,19 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>APR成都武侯大悦城</t>
+          <t>华为厦门思明星河COCO Park</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E99" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3319,19 +3319,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>APR北京顺义华联</t>
+          <t>APR成都金牛凯德</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E100" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -3346,19 +3346,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>APR成都武侯大悦城</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E101" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>APR北京旧宫万科</t>
+          <t>APR北京顺义华联</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E102" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -3400,19 +3400,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DJI上海百联又一城授权体验店</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E103" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>APR北京牡丹园翠微</t>
+          <t>APR北京旧宫万科</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E104" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -3454,19 +3454,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>APR北京丽泽龙湖</t>
+          <t>DJI上海百联又一城授权体验店</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E105" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -3481,19 +3481,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>华为北京北苑龙湖</t>
+          <t>APR北京牡丹园翠微</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E106" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -3508,19 +3508,19 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>APR北京丽泽龙湖</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -3535,19 +3535,19 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>APR北京石景山万达</t>
+          <t>华为北京北苑龙湖</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E108" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -3562,19 +3562,19 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>APR北京石景山喜隆多</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E109" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -3589,19 +3589,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>华为北京大兴大族</t>
+          <t>APR北京石景山万达</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E110" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>APR北京龙德广场</t>
+          <t>APR北京石景山喜隆多</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E111" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -3643,14 +3643,19 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DJI上海FFC滨江悦里授权体验店</t>
+          <t>华为北京大兴大族</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="E112" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -3665,7 +3670,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>APR北京颐堤港</t>
+          <t>APR北京龙德广场</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3674,10 +3679,10 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E113" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -3692,19 +3697,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DJI北京翠微百货授权体验店</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>北京飞航</t>
+          <t>DJI上海FFC滨江悦里授权体验店</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E114" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -3719,19 +3719,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>华为厦门思明宝龙一城</t>
+          <t>APR北京颐堤港</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E115" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -3746,19 +3746,19 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>APR成都高新伊藤</t>
+          <t>DJI北京翠微百货授权体验店</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E116" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -3773,19 +3773,19 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>华为北京平谷万达</t>
+          <t>华为厦门思明宝龙一城</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E117" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -3800,19 +3800,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>APR北京东坝万达</t>
+          <t>华为北京平谷万达</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E118" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -3827,19 +3827,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>APR成都金楠天街</t>
+          <t>APR北京东坝万达</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E119" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -3854,19 +3854,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>华为北京来福士</t>
+          <t>APR成都金楠天街</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E120" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -3881,19 +3881,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>APR北京望京华彩</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E121" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>APR北京房山龙湖</t>
+          <t>APR北京望京华彩</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E122" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -3935,19 +3935,19 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DJI北京龙湖熙悦天街授权体验店</t>
+          <t>APR北京房山龙湖</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E123" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
@@ -3962,19 +3962,19 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>华为厦门思明瑞景广场</t>
+          <t>DJI北京龙湖熙悦天街授权体验店</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E124" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -3989,19 +3989,19 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>APR北京望京凯德茂</t>
+          <t>华为厦门思明瑞景广场</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E125" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -4016,12 +4016,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>APR成都武侯吾悦</t>
+          <t>APR北京望京凯德茂</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4043,19 +4043,19 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>APR北京长安龙湖</t>
+          <t>APR成都武侯吾悦</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E127" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -4070,19 +4070,19 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>APR北京长安龙湖</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E128" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -4097,19 +4097,19 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>APR北京大兴龙湖</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E129" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>APR北京房山熙悦</t>
+          <t>APR北京大兴龙湖</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E130" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DJI北京长楹天街授权体验店</t>
+          <t>APR北京房山熙悦</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -4178,19 +4178,19 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>APR北京北苑龙湖</t>
+          <t>DJI北京长楹天街授权体验店</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E132" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -5450,7 +5450,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>150****2535</t>
+          <t>138****9886</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5473,7 +5473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>185****7000</t>
+          <t>150****2535</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>华为北京丰科万达</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5496,7 +5496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>136****4066</t>
+          <t>185****7000</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京丰科万达</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5519,7 +5519,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>138****9886</t>
+          <t>136****4066</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）带感绿</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6942103183102</t>
+          <t>6942103183133</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）带感绿</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6942103183133</t>
+          <t>6942103183102</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -11637,12 +11637,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -11747,12 +11747,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -12187,12 +12187,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -12242,12 +12242,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -12407,12 +12407,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -12462,12 +12462,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -12517,12 +12517,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -12572,12 +12572,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -12682,12 +12682,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -12902,12 +12902,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -13122,12 +13122,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -13177,12 +13177,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -13232,12 +13232,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -13342,12 +13342,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -13617,12 +13617,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -14277,12 +14277,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14332,12 +14332,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -14442,12 +14442,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -14552,12 +14552,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -14607,12 +14607,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -14662,12 +14662,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -14717,12 +14717,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -14827,12 +14827,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -14882,12 +14882,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -14937,12 +14937,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -15047,12 +15047,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -15212,12 +15212,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -15487,12 +15487,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -15542,12 +15542,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -15597,12 +15597,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K86" t="n">
@@ -15652,12 +15652,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -15872,12 +15872,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -15927,12 +15927,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -16147,12 +16147,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -16312,12 +16312,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -16367,12 +16367,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -16477,12 +16477,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -16587,12 +16587,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -16642,12 +16642,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -16697,12 +16697,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -17082,12 +17082,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -17137,12 +17137,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -17192,12 +17192,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -17247,12 +17247,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -17302,12 +17302,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -17522,12 +17522,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -17577,12 +17577,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -17742,12 +17742,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -17797,12 +17797,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -17852,12 +17852,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -17907,12 +17907,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -17962,12 +17962,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K129" t="n">
@@ -18017,12 +18017,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -18127,12 +18127,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -18292,12 +18292,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K135" t="n">
@@ -18347,12 +18347,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K136" t="n">
@@ -18457,12 +18457,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -18622,12 +18622,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K141" t="n">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K143" t="n">
@@ -18952,12 +18952,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -19117,12 +19117,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -19227,12 +19227,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -19282,12 +19282,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K153" t="n">
@@ -19337,12 +19337,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K154" t="n">
@@ -19447,12 +19447,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K156" t="n">
@@ -19502,12 +19502,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K158" t="n">
@@ -19612,12 +19612,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K159" t="n">
@@ -19722,12 +19722,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K161" t="n">
@@ -19887,12 +19887,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K164" t="n">
@@ -19942,12 +19942,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K165" t="n">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -20107,12 +20107,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K168" t="n">
@@ -20162,12 +20162,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K169" t="n">
@@ -20217,12 +20217,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K170" t="n">
@@ -20382,12 +20382,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00 （12GB+512GB）零度白</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>6942103183126</t>
+          <t>6942103183133</t>
         </is>
       </c>
       <c r="K173" t="n">
@@ -20437,12 +20437,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
+          <t>nova 15 Ultra SLY-AL00 （12GB+512GB）零度白</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>6942103183133</t>
+          <t>6942103183126</t>
         </is>
       </c>
       <c r="K174" t="n">
@@ -20547,12 +20547,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K176" t="n">
@@ -20602,12 +20602,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -20657,12 +20657,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152702</t>
         </is>
       </c>
       <c r="K178" t="n">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K179" t="n">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K180" t="n">
@@ -20822,12 +20822,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K181" t="n">
@@ -20877,12 +20877,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -20932,12 +20932,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>6942103152702</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K183" t="n">
@@ -21097,12 +21097,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K186" t="n">
@@ -21152,12 +21152,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -21262,12 +21262,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K189" t="n">
@@ -21317,12 +21317,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K190" t="n">
@@ -21427,12 +21427,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -21482,12 +21482,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K193" t="n">
@@ -21537,12 +21537,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K194" t="n">
@@ -21702,12 +21702,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -21812,12 +21812,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K199" t="n">
@@ -21867,12 +21867,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K200" t="n">
@@ -21922,12 +21922,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K201" t="n">
@@ -21977,12 +21977,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -22032,12 +22032,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K203" t="n">
@@ -22087,12 +22087,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K204" t="n">
@@ -22637,12 +22637,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K214" t="n">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K215" t="n">
@@ -22747,12 +22747,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K216" t="n">
@@ -22802,12 +22802,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -22857,12 +22857,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K218" t="n">
@@ -22912,12 +22912,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K219" t="n">
@@ -22967,12 +22967,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K220" t="n">
@@ -23242,12 +23242,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>EasyFit 2 曜石黑 氟橡胶表带 黑 演示样机</t>
+          <t>智选 艾优智能剃须刀 尊享款 H1钛金灰 演示样机</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>YJ6941487208418</t>
+          <t>YJ6970871389662</t>
         </is>
       </c>
       <c r="K225" t="n">
@@ -23297,12 +23297,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>智选 艾优智能剃须刀 尊享款 H1钛金灰 演示样机</t>
+          <t>EasyFit 2 曜石黑 氟橡胶表带 黑 演示样机</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>YJ6970871389662</t>
+          <t>YJ6941487208418</t>
         </is>
       </c>
       <c r="K226" t="n">
@@ -23517,12 +23517,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K230" t="n">
@@ -23572,12 +23572,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K231" t="n">
@@ -23682,12 +23682,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K233" t="n">
@@ -23737,12 +23737,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K234" t="n">
@@ -23847,12 +23847,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K236" t="n">
@@ -23902,12 +23902,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K237" t="n">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K238" t="n">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K239" t="n">
@@ -24122,12 +24122,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K241" t="n">
@@ -25607,17 +25607,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>TOMTOC Defender A14 城市简约手提电脑包</t>
+          <t>RECCI锐思 RHO-M25 折叠旋转 Mac 支架 灰色</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6970412220850</t>
+          <t>6955482541180</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -25678,17 +25678,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>鼠标和键盘</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M25 折叠旋转 Mac 支架 灰色</t>
+          <t>ZUER卓耳 四向滚轮三模无线鼠标</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6955482541180</t>
+          <t>6973620631524</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -25749,17 +25749,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 清薄键盘保护膜</t>
+          <t>HUNTKEY航嘉 USB-C 4合一 多功能扩展坞 黑色</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6922329934702</t>
+          <t>6946333017596</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -25820,17 +25820,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>鼠标和键盘</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ZUER卓耳 四向滚轮三模无线鼠标</t>
+          <t>TOMTOC Defender A14 城市简约手提电脑包</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6973620631524</t>
+          <t>6970412220850</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -25891,17 +25891,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>HUNTKEY航嘉 USB-C 4合一 多功能扩展坞 黑色</t>
+          <t>VOKAMO沃咔曼 清薄键盘保护膜</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6946333017596</t>
+          <t>6922329934702</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -26175,17 +26175,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
+          <t>VOKAMO 沃咔曼 iPhone 系列 3D 钻石高清三强钢化玻璃膜 黑 iPhone 17/17 Pro</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>195****10144</t>
+          <t>6922329935952</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -26246,17 +26246,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>VOKAMO 沃咔曼 iPhone 系列 3D 钻石高清三强钢化玻璃膜 黑 iPhone 17/17 Pro</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6922329935952</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -26322,12 +26322,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17 冰川减震磁吸肤感保护壳 磨砂透黑</t>
+          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6922329935587</t>
+          <t>6922329935921</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -26388,17 +26388,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
+          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6922329935921</t>
+          <t>195****10144</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -26530,17 +26530,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>VOKAMO沃咔曼 iPhone 17 冰川减震磁吸肤感保护壳 磨砂透黑</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6922329935587</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -26743,17 +26743,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 iPad Pro 11英寸 铂金系列 高清钢化玻璃膜</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6937045847984</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -26956,17 +26956,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>MOCOLL摩可 iPad Pro 11英寸 铂金系列 高清钢化玻璃膜</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6937045847984</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -27098,17 +27098,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPad 系列魔幻旋转防刮保护套</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6922329935303</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -27169,17 +27169,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
+          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6937045874478</t>
+          <t>6941876245338</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -27240,17 +27240,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6937045874478</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -27311,17 +27311,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
+          <t>VOKAMO沃咔曼 iPad 系列魔幻旋转防刮保护套</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6941876245338</t>
+          <t>6922329935303</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -27742,12 +27742,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6941876245444</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -27813,12 +27813,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>6941876245444</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -27950,17 +27950,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -28021,17 +28021,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4894222083837</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -28097,12 +28097,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 防偷窥防静电二强钢化膜 黑色</t>
+          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>6927123810382</t>
+          <t>4894222083837</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -28168,12 +28168,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>ZGA iPhone 17 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>6927123810382</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -30854,12 +30854,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Pura X Max 典藏版 HOP-AL10(16GB+1TB) 零度白</t>
+          <t>Pura X Max 典藏版 HOP-AL10(16GB+1TB) 幻夜黑</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>6942103195433</t>
+          <t>6942103195419</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -30925,12 +30925,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Pura X Max 典藏版 HOP-AL10(16GB+1TB) 幻夜黑</t>
+          <t>Pura X Max 典藏版 HOP-AL10(16GB+1TB) 零度白</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>6942103195419</t>
+          <t>6942103195433</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -31559,17 +31559,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>195****10144</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -31635,12 +31635,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 黑色 iPhone 17</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6927123810429</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -31701,17 +31701,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>195****10144</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -31772,17 +31772,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 黑色 iPhone 17</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>6927123810429</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -31848,12 +31848,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -31919,12 +31919,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -31985,17 +31985,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -32056,17 +32056,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>线缆</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>60W USB-C 充电线 (1 米) - 无塑料包装-MW493FE/A</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****71875</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -32127,17 +32127,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>线缆</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>60W USB-C 充电线 (1 米) - 无塑料包装-MW493FE/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>195****71875</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -32482,17 +32482,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>SWITCHEASYiPhone 系列 LenStand M 镜头支架防摔保护壳珊瑚 iPhone 17 Pro Max</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线 橙色</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>4895241136474</t>
+          <t>6922329936645</t>
         </is>
       </c>
       <c r="L106" t="n">
@@ -32553,17 +32553,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
+          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>6922329936577</t>
+          <t>6927123810405</t>
         </is>
       </c>
       <c r="L107" t="n">
@@ -32624,17 +32624,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线 橙色</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>6922329936645</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -32766,17 +32766,17 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -32837,17 +32837,17 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>SWITCHEASYiPhone 系列 LenStand M 镜头支架防摔保护壳珊瑚 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>4895241136474</t>
         </is>
       </c>
       <c r="L111" t="n">
@@ -32908,17 +32908,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>6927123810405</t>
+          <t>6922329936577</t>
         </is>
       </c>
       <c r="L112" t="n">
@@ -33263,17 +33263,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>6927123810559</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -33339,12 +33339,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -33405,17 +33405,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -33476,17 +33476,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -33547,17 +33547,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>6955482539477</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -33618,17 +33618,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -33689,17 +33689,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -33760,17 +33760,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
+          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>6927123810559</t>
+          <t>6955482539477</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -33831,17 +33831,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -33973,17 +33973,17 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>6955482539477</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -34044,17 +34044,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -34186,17 +34186,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6955482539477</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -34328,17 +34328,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>6927123810559</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -34399,17 +34399,17 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>CLEER可丽尔 ARC 6 开放式 AI 耳机 薄暮灰</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>6938741702959</t>
+          <t>6927123810559</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -34470,17 +34470,17 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>CLEER可丽尔 ARC 6 开放式 AI 耳机 薄暮灰</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6938741702959</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -34612,17 +34612,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -34754,17 +34754,17 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>MAGICPIX魔图极秀 iPhone 17 系列摄影课程 - 用 iPhone 拍照片</t>
+          <t>iPhone 17 Pro 256GB 银色 - MG8T4CH/A</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>XMPZ202612189</t>
+          <t>195****28869</t>
         </is>
       </c>
       <c r="L138" t="n">
@@ -34825,17 +34825,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro 256GB 银色 - MG8T4CH/A</t>
+          <t>MAGICPIX魔图极秀 iPhone 17 系列摄影课程 - 用 iPhone 拍照片</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>195****28869</t>
+          <t>XMPZ202612189</t>
         </is>
       </c>
       <c r="L139" t="n">
@@ -35395,12 +35395,12 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>11 英寸 iPad GPS 128GB/粉色-MD4E4CH/A</t>
+          <t>11 英寸 iPad GPS 128GB/蓝色-MD4A4CH/A</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>195****86836</t>
+          <t>195****86379</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -35463,12 +35463,12 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>11 英寸 iPad GPS 128GB/蓝色-MD4A4CH/A</t>
+          <t>11 英寸 iPad GPS 128GB/粉色-MD4E4CH/A</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>195****86379</t>
+          <t>195****86836</t>
         </is>
       </c>
       <c r="L148" t="n">
@@ -35526,17 +35526,17 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPad 高清保护膜</t>
+          <t>LIBRATONE小鸟音响 UP 耳机</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>6974623613036</t>
+          <t>6975324441119</t>
         </is>
       </c>
       <c r="L149" t="n">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
+          <t>RICHIC锐壳 iPad 高清保护膜</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>6942297127005</t>
+          <t>6974623613036</t>
         </is>
       </c>
       <c r="L150" t="n">
@@ -35668,17 +35668,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>LIBRATONE小鸟音响 UP 耳机</t>
+          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>6975324441119</t>
+          <t>6942297127005</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -35815,12 +35815,12 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPad 高清保护膜</t>
+          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>6974623613036</t>
+          <t>6942297127012</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -35886,12 +35886,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
+          <t>RICHIC锐壳 iPad 高清保护膜</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>6942297127012</t>
+          <t>6974623613036</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -36094,17 +36094,17 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>音乐</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
+          <t>AirPods 4 (支持主动降噪)-MXP93CH/A</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>6941876245437</t>
+          <t>195****89550</t>
         </is>
       </c>
       <c r="L157" t="n">
@@ -36165,17 +36165,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>音乐</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>AirPods 4 (支持主动降噪)-MXP93CH/A</t>
+          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>195****89550</t>
+          <t>6941876245437</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -39633,17 +39633,17 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L207" t="n">
@@ -39704,17 +39704,17 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>195****10144</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L208" t="n">
@@ -39775,17 +39775,17 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>195****10144</t>
         </is>
       </c>
       <c r="L209" t="n">
@@ -39846,17 +39846,17 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L210" t="n">
@@ -39922,12 +39922,12 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L211" t="n">
@@ -40414,17 +40414,17 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L218" t="n">
@@ -40485,17 +40485,17 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L219" t="n">
@@ -40556,17 +40556,17 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L220" t="n">
@@ -40845,12 +40845,12 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 黑色</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>4894222083820</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L224" t="n">
@@ -40911,17 +40911,17 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>RICHIC锐壳 氮化镓三口充电器 65W</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6974623613029</t>
         </is>
       </c>
       <c r="L225" t="n">
@@ -41053,17 +41053,17 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 氮化镓三口充电器 65W</t>
+          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 黑色</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>6974623613029</t>
+          <t>4894222083820</t>
         </is>
       </c>
       <c r="L227" t="n">
@@ -41124,17 +41124,17 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 橙色</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>6928288500057</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L228" t="n">
@@ -41266,17 +41266,17 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 橙色</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>6928288500057</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -41697,18 +41697,15 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Osmo Pocket 4P 标准套装</t>
+          <t>DJI Care 随心换 1年版（Osmo Pocket 4P）中国版</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>6937224148321</t>
+          <t>6937224151062</t>
         </is>
       </c>
       <c r="L236" t="n">
-        <v>1</v>
-      </c>
-      <c r="M236" t="n">
         <v>1</v>
       </c>
       <c r="N236" t="n">
@@ -41779,6 +41776,9 @@
       <c r="L237" t="n">
         <v>1</v>
       </c>
+      <c r="M237" t="n">
+        <v>1</v>
+      </c>
       <c r="N237" t="n">
         <v>8235</v>
       </c>
@@ -41831,17 +41831,17 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Pocket</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>Osmo Pocket 4P 标准套装</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224148321</t>
         </is>
       </c>
       <c r="L238" t="n">
@@ -41983,6 +41983,9 @@
       <c r="L240" t="n">
         <v>1</v>
       </c>
+      <c r="M240" t="n">
+        <v>1</v>
+      </c>
       <c r="N240" t="n">
         <v>8235</v>
       </c>
@@ -42035,23 +42038,20 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Pocket</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo Pocket 4P）中国版</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>6937224151062</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L241" t="n">
-        <v>1</v>
-      </c>
-      <c r="M241" t="n">
         <v>1</v>
       </c>
       <c r="N241" t="n">
@@ -43957,12 +43957,12 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 白色</t>
+          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 黑色</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>6941487218011</t>
+          <t>6941487218028</t>
         </is>
       </c>
       <c r="L268" t="n">
@@ -44312,12 +44312,12 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 黑色</t>
+          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 白色</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>6941487218028</t>
+          <t>6941487218011</t>
         </is>
       </c>
       <c r="L273" t="n">
@@ -45296,17 +45296,17 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>表带</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>SWITCHEASY Apple Watch 系列 Mesh 不锈钢磁扣表带</t>
+          <t>COMMA珂玛  盾威系列全屏 Apple Watch 46mm 保护膜 V3</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>6977503191334</t>
+          <t>6942297146426</t>
         </is>
       </c>
       <c r="L287" t="n">
@@ -45367,17 +45367,17 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>表带</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>COMMA珂玛  盾威系列全屏 Apple Watch 46mm 保护膜 V3</t>
+          <t>SWITCHEASY Apple Watch 系列 Mesh 不锈钢磁扣表带</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>6942297146426</t>
+          <t>6977503191334</t>
         </is>
       </c>
       <c r="L288" t="n">
@@ -45438,17 +45438,17 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L289" t="n">
@@ -45509,17 +45509,17 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>ZGA iPhone 17e 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6927123814069</t>
         </is>
       </c>
       <c r="L290" t="n">
@@ -45585,12 +45585,12 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17e 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>6927123814069</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L291" t="n">
@@ -46153,12 +46153,12 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPad 高清保护膜</t>
+          <t>VOKAMO沃咔曼 iPad Air 魔幻旋转防刮保护套</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>6974623613036</t>
+          <t>6922329934283</t>
         </is>
       </c>
       <c r="L299" t="n">
@@ -46219,17 +46219,17 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
+          <t>RICHIC锐壳 iPad 高清保护膜</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>6941876245338</t>
+          <t>6974623613036</t>
         </is>
       </c>
       <c r="L300" t="n">
@@ -46290,17 +46290,17 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPad Air 魔幻旋转防刮保护套</t>
+          <t>LIBRATONE小鸟音响 UP 耳机</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>6922329934283</t>
+          <t>6975324441119</t>
         </is>
       </c>
       <c r="L301" t="n">
@@ -46361,17 +46361,17 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>LIBRATONE小鸟音响 UP 耳机</t>
+          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>6975324441119</t>
+          <t>6941876245338</t>
         </is>
       </c>
       <c r="L302" t="n">
@@ -46574,17 +46574,17 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L305" t="n">
@@ -46645,17 +46645,17 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L306" t="n">
@@ -46716,17 +46716,17 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L307" t="n">
@@ -46787,17 +46787,17 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L308" t="n">
@@ -50449,17 +50449,17 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>MatePad pro</t>
+          <t>运营商卡号</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>MatePad Pro 12.2寸 MRO-W00(12GB+512GB) 砚黑</t>
+          <t>橙分期团购合约-129-24（终端直降1170）</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>6942103130816</t>
+          <t>811094496</t>
         </is>
       </c>
       <c r="L360" t="n">
@@ -50520,17 +50520,17 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>运营商卡号</t>
+          <t>MatePad pro</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>橙分期团购合约-129-24（终端直降1170）</t>
+          <t>MatePad Pro 12.2寸 MRO-W00(12GB+512GB) 砚黑</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>811094496</t>
+          <t>6942103130816</t>
         </is>
       </c>
       <c r="L361" t="n">
